--- a/data/trans_bre/P1432-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1432-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,22</t>
+          <t>-2,03; 0,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,82</t>
+          <t>-0,1; 2,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,67</t>
+          <t>-0,65; 1,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,22 +714,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,53</t>
+          <t>-1,59; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,0</t>
+          <t>-1,23; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,11</t>
+          <t>-0,38; 3,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-85,02; 441,09</t>
+          <t>-82,9; 335,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -794,27 +794,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,28</t>
+          <t>-1,38; 3,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,75</t>
+          <t>-1,47; 1,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,01</t>
+          <t>-0,65; 3,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 830,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 339,41</t>
+          <t>-100,0; 373,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,5</t>
+          <t>-1,29; 0,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,69</t>
+          <t>-1,0; 0,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,75</t>
+          <t>0,02; 1,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,27; 75,76</t>
+          <t>-77,43; 55,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,3; 158,74</t>
+          <t>-83,61; 234,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 1043,75</t>
+          <t>-20,08; 895,03</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,99</t>
+          <t>-1,1; 2,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,74</t>
+          <t>0,81; 3,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,07</t>
+          <t>-0,98; 1,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 341,53</t>
+          <t>-60,51; 332,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,29; 1733,35</t>
+          <t>30,98; 1577,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-70,58; 214,43</t>
+          <t>-67,73; 216,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,06</t>
+          <t>1,35; 3,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,39</t>
+          <t>1,45; 3,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,46</t>
+          <t>1,48; 3,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,94</t>
+          <t>-0,17; 0,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,53</t>
+          <t>0,4; 1,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,43</t>
+          <t>0,44; 1,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 111,1</t>
+          <t>-12,42; 111,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,57; 324,65</t>
+          <t>38,63; 331,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,55; 385,24</t>
+          <t>59,07; 382,31</t>
         </is>
       </c>
     </row>
